--- a/tests/fixtures/catalogo.xlsx
+++ b/tests/fixtures/catalogo.xlsx
@@ -11,12 +11,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
-      <c r="A1">
-        <v>C</v>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Catalogo biblioteca comunale</t>
         </is>
       </c>
     </row>
@@ -33,20 +30,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Anno</t>
+          <t>Prestato a</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Collocazione</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>ISBN</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
         <is>
           <t>Stato conservazione</t>
         </is>
@@ -63,20 +55,17 @@
           <t>Euclide</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1482</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ipazia</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>copia rilegata</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>978-88-06-12345-6</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t>buono</t>
         </is>
@@ -85,7 +74,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gli Elementi</t>
+          <t>Elementi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -93,20 +82,7 @@
           <t>Euclide</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1482</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
-        <is>
-          <t>9788806123456</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
         <is>
           <t>buono</t>
         </is>
@@ -123,15 +99,12 @@
           <t>Tolomeo</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1515</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>Eratostene</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>discreto</t>
         </is>
